--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260727.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260727.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.41%</t>
+          <t>10.39%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.28%</t>
+          <t>8.37%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.05%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>5.86%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.37%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.30%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.22%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.19%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>4.86%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.07%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.88%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.65%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>4,706,000</t>
+          <t>528,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>528,000</t>
+          <t>4,706,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1210,73 +1210,73 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,646,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>2,966,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,966,000</t>
+          <t>2,280,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>10,203,013,754</t>
+          <t>10,125,827,798</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-7,044,281</t>
+          <t>-735,570,483</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
